--- a/ksoft_old/docs/records/Supplier_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Supplier_Group_Records.xlsx
@@ -1480,13 +1480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C08B3C78-62D9-4D62-8492-965AEDFE27FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B35D6F3-2BA2-4102-BF58-2FC93CC9499E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B7C0CFE-0E40-414D-94BA-962DB5BFCF4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA96A20-ACBB-4CA9-8721-CAE4182E0457}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0CD4838-81E9-4F5A-8506-6C51FBDB667A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CC18759-E332-4519-A75F-04D50949E16F}"/>
 </file>
--- a/ksoft_old/docs/records/Supplier_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Supplier_Group_Records.xlsx
@@ -1480,13 +1480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B35D6F3-2BA2-4102-BF58-2FC93CC9499E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DADB2F-B82E-42F7-88F9-6F7CD9420D8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA96A20-ACBB-4CA9-8721-CAE4182E0457}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BD62DD-F636-4A37-A7A0-88D17C16E4C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CC18759-E332-4519-A75F-04D50949E16F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA3F228D-B00B-4367-BD0B-CB6C97428BFD}"/>
 </file>
--- a/ksoft_old/docs/records/Supplier_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Supplier_Group_Records.xlsx
@@ -1480,13 +1480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DADB2F-B82E-42F7-88F9-6F7CD9420D8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C08B3C78-62D9-4D62-8492-965AEDFE27FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BD62DD-F636-4A37-A7A0-88D17C16E4C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B7C0CFE-0E40-414D-94BA-962DB5BFCF4A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA3F228D-B00B-4367-BD0B-CB6C97428BFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0CD4838-81E9-4F5A-8506-6C51FBDB667A}"/>
 </file>